--- a/CNN/CNN.xlsx
+++ b/CNN/CNN.xlsx
@@ -5,24 +5,63 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\조근하\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54373D2E-E44A-4334-80CB-F68DF2ED1F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D4ED05-DC9B-4B66-81FF-4EECC184B0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="cnn_kernel" sheetId="2" r:id="rId1"/>
+    <sheet name="cnn_hole_detector" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>1D</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  CNN 합성곱(Convolution) &amp; 구멍 감지(Hole Detector) 시뮬레이터</t>
+  </si>
+  <si>
+    <t>■ 1. 입력 이미지 (숫자 '6' 데이터)</t>
+  </si>
+  <si>
+    <t>■ 2. 구멍 감지 필터 (Kernel)</t>
+  </si>
+  <si>
+    <t>■ 3. 활성화 함수 (ReLU)</t>
+  </si>
+  <si>
+    <t>■ 4. 출력 특성 맵 (Feature Map)</t>
+  </si>
+  <si>
+    <t>공식: f(x) = MAX(0, x)</t>
+  </si>
+  <si>
+    <t>설명: 합성곱 연산 결과가</t>
+  </si>
+  <si>
+    <t>음수이면 0, 양수이면</t>
+  </si>
+  <si>
+    <t>그대로 통과시킵니다.</t>
+  </si>
+  <si>
+    <t>💡 이미지 속 초록색 선과 하늘색(Cyan) 칸의 의미
+1. 가운데 노란색 필터는 테두리가 1이고 중심이 -10인 '구멍 감지 필터(Hole Detector)'입니다.
+2. 입력 이미지에서 숫자 '6'의 아랫부분(초록색 동그라미 영역)을 보면 주변은 1(흰색)인데 중심만 0(검은색 빈공간)인 완벽한 구멍 구조를 가집니다.
+3. 이 필터가 해당 구멍 영역을 지나갈 때 필터의 특성과 정확히 일치하여 가장 높은 결과값(8)을 출력하게 됩니다.
+4. 오른쪽 특성 맵에서 하늘색(Cyan)으로 채워진 칸이 바로 필터가 구멍을 성공적으로 감지해내어 강한 신호를 발생시킨 지점입니다.</t>
+  </si>
+  <si>
+    <t>■ 1. 입력 이미지 (숫자 '9' 데이터)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -30,7 +69,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -58,16 +97,105 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF203A43"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F2027"/>
+        <bgColor rgb="FF0F2027"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1A1A"/>
+        <bgColor rgb="FF1A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F7F6"/>
+        <bgColor rgb="FFF4F7F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FFF4F7F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor rgb="FFF4F7F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -75,15 +203,145 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -307,9 +565,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="B2:Y49"/>
-  <sheetFormatPr defaultColWidth="6.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="2" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:25">
       <c r="B2" s="2">
         <f>1</f>
         <v>1</v>
@@ -368,7 +626,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:25">
       <c r="B3" s="2">
         <f t="shared" ref="B3:I3" si="2">B2+1</f>
         <v>2</v>
@@ -427,7 +685,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:25">
       <c r="B4" s="2">
         <f t="shared" ref="B4:I4" si="4">B3+1</f>
         <v>3</v>
@@ -486,7 +744,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:25">
       <c r="B5" s="2">
         <f t="shared" ref="B5:I5" si="6">B4+1</f>
         <v>4</v>
@@ -545,7 +803,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:25">
       <c r="B6" s="2">
         <f t="shared" ref="B6:I6" si="8">B5+1</f>
         <v>5</v>
@@ -604,7 +862,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:25">
       <c r="B7" s="2">
         <f t="shared" ref="B7:I7" si="10">B6+1</f>
         <v>6</v>
@@ -672,7 +930,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:25">
       <c r="B8" s="2">
         <f t="shared" ref="B8:I8" si="12">B7+1</f>
         <v>7</v>
@@ -740,7 +998,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:25">
       <c r="B9" s="2">
         <f t="shared" ref="B9:I9" si="14">B8+1</f>
         <v>8</v>
@@ -808,7 +1066,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:25">
       <c r="B10" s="2">
         <f t="shared" ref="B10:I10" si="16">B9+1</f>
         <v>9</v>
@@ -867,7 +1125,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:25">
       <c r="B11" s="2">
         <f t="shared" ref="B11:I11" si="18">B10+1</f>
         <v>10</v>
@@ -926,7 +1184,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:25">
       <c r="B12" s="2">
         <f t="shared" ref="B12:I12" si="20">B11+1</f>
         <v>11</v>
@@ -985,7 +1243,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:25">
       <c r="B13" s="2">
         <f t="shared" ref="B13:I13" si="22">B12+1</f>
         <v>12</v>
@@ -1044,7 +1302,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:25">
       <c r="B14" s="2">
         <f t="shared" ref="B14:I14" si="24">B13+1</f>
         <v>13</v>
@@ -1103,7 +1361,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:25">
       <c r="B15" s="2">
         <f t="shared" ref="B15:I15" si="26">B14+1</f>
         <v>14</v>
@@ -1137,7 +1395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:25">
       <c r="B16" s="2">
         <f t="shared" ref="B16:I16" si="27">B15+1</f>
         <v>15</v>
@@ -1171,7 +1429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:20">
       <c r="I19" s="3" t="s">
         <v>0</v>
       </c>
@@ -1209,91 +1467,91 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="9:20">
       <c r="T20" s="1">
         <f t="shared" si="28"/>
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="9:20">
       <c r="T21" s="1">
         <f t="shared" si="28"/>
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="9:20">
       <c r="T22" s="1">
         <f t="shared" si="28"/>
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="9:20">
       <c r="T23" s="1">
         <f t="shared" si="28"/>
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="9:20">
       <c r="T24" s="1">
         <f t="shared" si="28"/>
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="9:20">
       <c r="T25" s="1">
         <f t="shared" si="28"/>
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="9:20">
       <c r="T26" s="1">
         <f t="shared" si="28"/>
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="9:20">
       <c r="T27" s="1">
         <f t="shared" si="28"/>
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="9:20">
       <c r="T28" s="1">
         <f t="shared" si="28"/>
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="9:20">
       <c r="T29" s="1">
         <f t="shared" si="28"/>
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="9:20">
       <c r="T30" s="1">
         <f t="shared" si="28"/>
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="9:20">
       <c r="T31" s="1">
         <f t="shared" si="28"/>
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="9:20">
       <c r="T32" s="1">
         <f t="shared" si="28"/>
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:20">
       <c r="T33" s="1">
         <f t="shared" si="28"/>
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="9:20">
       <c r="I36" s="3" t="s">
         <v>0</v>
       </c>
@@ -1330,7 +1588,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:20">
       <c r="K37" s="2">
         <v>0</v>
       </c>
@@ -1364,73 +1622,73 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:20">
       <c r="T38" s="1">
         <f t="shared" si="29"/>
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:20">
       <c r="T39" s="1">
         <f t="shared" si="29"/>
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:20">
       <c r="T40" s="1">
         <f t="shared" si="29"/>
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:20">
       <c r="T41" s="1">
         <f t="shared" si="29"/>
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:20">
       <c r="T42" s="1">
         <f t="shared" si="29"/>
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="9:20">
       <c r="T43" s="1">
         <f t="shared" si="29"/>
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="9:20">
       <c r="T44" s="1">
         <f t="shared" si="29"/>
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="9:20">
       <c r="T45" s="1">
         <f t="shared" si="29"/>
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="9:20">
       <c r="T46" s="1">
         <f t="shared" si="29"/>
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="9:20">
       <c r="T47" s="1">
         <f t="shared" si="29"/>
         <v>128</v>
       </c>
     </row>
-    <row r="48" spans="9:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="9:20">
       <c r="T48" s="1">
         <f t="shared" si="29"/>
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="20:20">
       <c r="T49" s="1">
         <f t="shared" si="29"/>
         <v>144</v>
@@ -1440,4 +1698,622 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4C1C38-35F1-46F7-9E10-BAE9E735E1FC}">
+  <dimension ref="A1:Q28"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="9" width="6.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" customWidth="1"/>
+    <col min="16" max="17" width="11.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="4" spans="1:17" ht="19.2">
+      <c r="A4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A5" s="7">
+        <v>0</v>
+      </c>
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="11">
+        <f>MAX(0,SUMPRODUCT(A5:C7,$G$5:$I$7))</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="11">
+        <f t="shared" ref="N5:O9" si="0">MAX(0,SUMPRODUCT(B5:D7,$G$5:$I$7))</f>
+        <v>5</v>
+      </c>
+      <c r="O5" s="11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A6" s="7">
+        <v>0</v>
+      </c>
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9">
+        <v>-10</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="11">
+        <f t="shared" ref="M6:M9" si="1">MAX(0,SUMPRODUCT(A6:C8,$G$5:$I$7))</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O6" s="11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A7" s="7">
+        <v>0</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A8" s="7">
+        <v>0</v>
+      </c>
+      <c r="B8" s="8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="21">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="O8" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A9" s="7">
+        <v>0</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A10" s="7">
+        <v>0</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A11" s="7">
+        <v>0</v>
+      </c>
+      <c r="B11" s="7">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="15"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="16"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="17"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="16"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="17"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="16"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="17"/>
+    </row>
+    <row r="18" spans="1:17" ht="39" customHeight="1">
+      <c r="A18" s="18"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="20"/>
+    </row>
+    <row r="21" spans="1:17" ht="19.2">
+      <c r="A21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A22" s="7">
+        <v>0</v>
+      </c>
+      <c r="B22" s="8">
+        <v>1</v>
+      </c>
+      <c r="C22" s="8">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>1</v>
+      </c>
+      <c r="H22" s="9">
+        <v>1</v>
+      </c>
+      <c r="I22" s="9">
+        <v>1</v>
+      </c>
+      <c r="K22" s="10"/>
+      <c r="M22" s="11">
+        <f>MAX(0,SUMPRODUCT(A22:C24,$G$5:$I$7))</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="21">
+        <f t="shared" ref="N22:N26" si="2">MAX(0,SUMPRODUCT(B22:D24,$G$5:$I$7))</f>
+        <v>8</v>
+      </c>
+      <c r="O22" s="11">
+        <f t="shared" ref="O22:O26" si="3">MAX(0,SUMPRODUCT(C22:E24,$G$5:$I$7))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A23" s="7">
+        <v>0</v>
+      </c>
+      <c r="B23" s="8">
+        <v>1</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <v>1</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>1</v>
+      </c>
+      <c r="H23" s="9">
+        <v>-10</v>
+      </c>
+      <c r="I23" s="9">
+        <v>1</v>
+      </c>
+      <c r="K23" s="12"/>
+      <c r="M23" s="11">
+        <f t="shared" ref="M23:M26" si="4">MAX(0,SUMPRODUCT(A23:C25,$G$5:$I$7))</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A24" s="7">
+        <v>0</v>
+      </c>
+      <c r="B24" s="8">
+        <v>1</v>
+      </c>
+      <c r="C24" s="8">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8">
+        <v>1</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>1</v>
+      </c>
+      <c r="H24" s="9">
+        <v>1</v>
+      </c>
+      <c r="I24" s="9">
+        <v>1</v>
+      </c>
+      <c r="K24" s="12"/>
+      <c r="M24" s="11">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="N24" s="11">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="O24" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A25" s="7">
+        <v>0</v>
+      </c>
+      <c r="B25" s="7">
+        <v>0</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <v>1</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0</v>
+      </c>
+      <c r="K25" s="12"/>
+      <c r="M25" s="11">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="N25" s="22">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="O25" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A26" s="7">
+        <v>0</v>
+      </c>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0</v>
+      </c>
+      <c r="D26" s="8">
+        <v>1</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0</v>
+      </c>
+      <c r="M26" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A27" s="7">
+        <v>0</v>
+      </c>
+      <c r="B27" s="8">
+        <v>1</v>
+      </c>
+      <c r="C27" s="8">
+        <v>1</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="22.8" customHeight="1">
+      <c r="A28" s="7">
+        <v>0</v>
+      </c>
+      <c r="B28" s="7">
+        <v>0</v>
+      </c>
+      <c r="C28" s="7">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:Q2"/>
+    <mergeCell ref="A14:Q18"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CNN/CNN.xlsx
+++ b/CNN/CNN.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D4ED05-DC9B-4B66-81FF-4EECC184B0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB2AE644-F527-457E-8C85-7D9182A38173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="cnn_kernel" sheetId="2" r:id="rId1"/>
-    <sheet name="cnn_hole_detector" sheetId="3" r:id="rId2"/>
+    <sheet name="convolution" sheetId="4" r:id="rId1"/>
+    <sheet name="cnn_kernel" sheetId="2" r:id="rId2"/>
+    <sheet name="cnn_hole_detector" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>1D</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -64,12 +78,89 @@
     <t>■ 1. 입력 이미지 (숫자 '9' 데이터)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(X)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(Y)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Total </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>X / Y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">P(X, Y) = P(X)*P(Y), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서로 독립</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marginal distribution</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Joint Distribution</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z = X + Y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(Z)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t># of Z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Convolution Random Variable Z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequency of Z = X  +  Y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <numFmts count="3">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="183" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -144,8 +235,37 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -194,8 +314,14 @@
         <bgColor rgb="FFF4F7F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -298,19 +424,127 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -326,6 +560,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -336,14 +580,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -359,8 +649,2757 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.655599300087489E-2"/>
+          <c:y val="0.14861111111111111"/>
+          <c:w val="0.86733289588801399"/>
+          <c:h val="0.73111111111111116"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>convolution!$A$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P(Z)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>convolution!$B$25:$L$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>convolution!$B$27:$L$27</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2.7777777777777776E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5555555555555552E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.3333333333333329E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.1111111111111111</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1388888888888889</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1388888888888889</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1111111111111111</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.3333333333333329E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.5555555555555552E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.7777777777777776E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2218-4DE6-BA5E-EF85CA2A0BA6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1115693135"/>
+        <c:axId val="1115688815"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1115693135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115688815"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1115688815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115693135"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.16627708326662383"/>
+          <c:y val="0.27717544353703188"/>
+          <c:w val="0.77152770060405829"/>
+          <c:h val="0.52790763165305543"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>convolution!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P(X)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>convolution!$B$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>convolution!$B$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4218-4DD9-9DBF-3B40B9234E29}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1115687855"/>
+        <c:axId val="1115680175"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1115687855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115680175"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1115680175"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115687855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>convolution!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P(Y)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>convolution!$B$6:$G$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>convolution!$B$7:$G$7</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5305-4673-B28D-FA4DCE9E6596}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1115690735"/>
+        <c:axId val="1115696975"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1115690735"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115696975"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1115696975"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1115690735"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>69292</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47523</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>660593</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>183174</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DE332CF-B197-6285-9792-3DA8C94A2423}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4230984" y="487138"/>
+          <a:ext cx="1008936" cy="1014882"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>271095</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>146537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>51288</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>219807</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="차트 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BE4ECC6-708D-B9BB-374D-38AF57DE7D9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>249116</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>124557</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>46161</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>148343</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="차트 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C183181-BECE-69B7-D318-80D56AB78DA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>146540</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>123092</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>373673</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>168519</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="차트 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E0AD48F-E235-A6CA-B445-6FD64D01C606}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,12 +3599,773 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{262ABAFE-AF6D-4F6C-8747-0E71FF37AA1F}">
+  <dimension ref="A2:T27"/>
+  <sheetFormatPr defaultRowHeight="17.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" style="24" customWidth="1"/>
+    <col min="2" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A2" s="30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A3" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="28">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28">
+        <v>2</v>
+      </c>
+      <c r="D3" s="28">
+        <v>3</v>
+      </c>
+      <c r="E3" s="28">
+        <v>4</v>
+      </c>
+      <c r="F3" s="28">
+        <v>5</v>
+      </c>
+      <c r="G3" s="28">
+        <v>6</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A4" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="25">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C4" s="25">
+        <f t="shared" ref="C4:G4" si="0">1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D4" s="25">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E4" s="25">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F4" s="25">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G4" s="25">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H4" s="26">
+        <f>SUM(B4:G4)</f>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A5"/>
+    </row>
+    <row r="6" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A6" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="28">
+        <v>1</v>
+      </c>
+      <c r="C6" s="28">
+        <v>2</v>
+      </c>
+      <c r="D6" s="28">
+        <v>3</v>
+      </c>
+      <c r="E6" s="28">
+        <v>4</v>
+      </c>
+      <c r="F6" s="28">
+        <v>5</v>
+      </c>
+      <c r="G6" s="28">
+        <v>6</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A7" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="25">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C7" s="25">
+        <f t="shared" ref="C7:G7" si="1">1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D7" s="25">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E7" s="25">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F7" s="25">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="G7" s="25">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H7" s="26">
+        <f>SUM(B7:G7)</f>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A10" s="54"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="55"/>
+      <c r="Q10" s="55"/>
+      <c r="R10" s="55"/>
+      <c r="S10" s="55"/>
+      <c r="T10" s="55"/>
+    </row>
+    <row r="12" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A12" s="30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A13" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A14" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="35">
+        <v>1</v>
+      </c>
+      <c r="C14" s="35">
+        <v>2</v>
+      </c>
+      <c r="D14" s="35">
+        <v>3</v>
+      </c>
+      <c r="E14" s="35">
+        <v>4</v>
+      </c>
+      <c r="F14" s="35">
+        <v>5</v>
+      </c>
+      <c r="G14" s="35">
+        <v>6</v>
+      </c>
+      <c r="L14" s="35">
+        <v>1</v>
+      </c>
+      <c r="M14" s="35">
+        <v>2</v>
+      </c>
+      <c r="N14" s="35">
+        <v>3</v>
+      </c>
+      <c r="O14" s="35">
+        <v>4</v>
+      </c>
+      <c r="P14" s="35">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A15" s="28">
+        <v>1</v>
+      </c>
+      <c r="B15" s="36">
+        <f>1/6^2</f>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="C15" s="37">
+        <f t="shared" ref="C15:G20" si="2">1/6^2</f>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="D15" s="37">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="E15" s="37">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="F15" s="37">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G15" s="38">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="H15" s="32">
+        <f>SUM(B15:G15)</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="K15" s="28">
+        <v>1</v>
+      </c>
+      <c r="L15" s="45">
+        <f>$K15+L$14</f>
+        <v>2</v>
+      </c>
+      <c r="M15" s="46">
+        <f t="shared" ref="M15:Q20" si="3">$K15+M$14</f>
+        <v>3</v>
+      </c>
+      <c r="N15" s="46">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="O15" s="46">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P15" s="46">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="Q15" s="47">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="17.25" customHeight="1">
+      <c r="A16" s="28">
+        <v>2</v>
+      </c>
+      <c r="B16" s="39">
+        <f t="shared" ref="B16:B20" si="4">1/6^2</f>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="C16" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="D16" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="E16" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="F16" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G16" s="41">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="H16" s="32">
+        <f t="shared" ref="H16:H20" si="5">SUM(B16:G16)</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="K16" s="28">
+        <v>2</v>
+      </c>
+      <c r="L16" s="48">
+        <f t="shared" ref="L16:L20" si="6">$K16+L$14</f>
+        <v>3</v>
+      </c>
+      <c r="M16" s="35">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="N16" s="35">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="O16" s="35">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="P16" s="35">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="Q16" s="49">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A17" s="28">
+        <v>3</v>
+      </c>
+      <c r="B17" s="39">
+        <f t="shared" si="4"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="C17" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="D17" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="E17" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="F17" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G17" s="41">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="H17" s="32">
+        <f t="shared" si="5"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="K17" s="28">
+        <v>3</v>
+      </c>
+      <c r="L17" s="48">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="M17" s="35">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="N17" s="35">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="O17" s="35">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="P17" s="35">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="Q17" s="49">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A18" s="28">
+        <v>4</v>
+      </c>
+      <c r="B18" s="39">
+        <f t="shared" si="4"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="C18" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="D18" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="E18" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="F18" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G18" s="41">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="H18" s="32">
+        <f t="shared" si="5"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="K18" s="28">
+        <v>4</v>
+      </c>
+      <c r="L18" s="48">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="M18" s="35">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="N18" s="35">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="O18" s="35">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="P18" s="35">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="Q18" s="49">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A19" s="28">
+        <v>5</v>
+      </c>
+      <c r="B19" s="39">
+        <f t="shared" si="4"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="C19" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="D19" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="E19" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="F19" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G19" s="41">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="H19" s="32">
+        <f t="shared" si="5"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="K19" s="28">
+        <v>5</v>
+      </c>
+      <c r="L19" s="48">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="M19" s="35">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="N19" s="35">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="O19" s="35">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="P19" s="35">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="Q19" s="49">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A20" s="28">
+        <v>6</v>
+      </c>
+      <c r="B20" s="42">
+        <f t="shared" si="4"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="C20" s="43">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="D20" s="43">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="E20" s="43">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="F20" s="43">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G20" s="44">
+        <f t="shared" si="2"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="H20" s="32">
+        <f t="shared" si="5"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="K20" s="28">
+        <v>6</v>
+      </c>
+      <c r="L20" s="50">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="M20" s="51">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="N20" s="51">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="O20" s="51">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="P20" s="51">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="Q20" s="52">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="17.25" customHeight="1">
+      <c r="B21" s="31">
+        <f>SUM(B15:B20)</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="C21" s="31">
+        <f t="shared" ref="C21:G21" si="7">SUM(C15:C20)</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="D21" s="31">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="E21" s="31">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="F21" s="31">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="G21" s="31">
+        <f t="shared" si="7"/>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="H21" s="32">
+        <f>SUM(B15:G20)</f>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="17.25" customHeight="1">
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A23" s="30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A24" s="29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A25" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="28">
+        <v>2</v>
+      </c>
+      <c r="C25" s="28">
+        <v>3</v>
+      </c>
+      <c r="D25" s="28">
+        <v>4</v>
+      </c>
+      <c r="E25" s="28">
+        <v>5</v>
+      </c>
+      <c r="F25" s="28">
+        <v>6</v>
+      </c>
+      <c r="G25" s="28">
+        <v>7</v>
+      </c>
+      <c r="H25" s="28">
+        <v>8</v>
+      </c>
+      <c r="I25" s="28">
+        <v>9</v>
+      </c>
+      <c r="J25" s="28">
+        <v>10</v>
+      </c>
+      <c r="K25" s="28">
+        <v>11</v>
+      </c>
+      <c r="L25" s="28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A26" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <f>COUNTIF($L$15:$Q$20, B25)</f>
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ref="C26:L26" si="8">COUNTIF($L$15:$Q$20, C25)</f>
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A27" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="31">
+        <f>B26/COUNT($L$15:$Q$20)</f>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="C27" s="31">
+        <f t="shared" ref="C27:L27" si="9">C26/COUNT($L$15:$Q$20)</f>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="D27" s="31">
+        <f t="shared" si="9"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E27" s="31">
+        <f t="shared" si="9"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F27" s="31">
+        <f t="shared" si="9"/>
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="G27" s="31">
+        <f t="shared" si="9"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H27" s="31">
+        <f t="shared" si="9"/>
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="I27" s="31">
+        <f t="shared" si="9"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J27" s="31">
+        <f t="shared" si="9"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="K27" s="31">
+        <f t="shared" si="9"/>
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="L27" s="31">
+        <f t="shared" si="9"/>
+        <v>2.7777777777777776E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="B2:Y49"/>
-  <sheetFormatPr defaultColWidth="6.44140625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="6.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="2" spans="2:25">
       <c r="B2" s="2">
@@ -1700,611 +5500,611 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4C1C38-35F1-46F7-9E10-BAE9E735E1FC}">
   <dimension ref="A1:Q28"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="5" width="5.5546875" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="9" width="6.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" customWidth="1"/>
-    <col min="16" max="17" width="11.109375" customWidth="1"/>
+    <col min="1" max="5" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" customWidth="1"/>
+    <col min="16" max="17" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
+      <c r="A1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-    </row>
-    <row r="4" spans="1:17" ht="19.2">
-      <c r="A4" s="6" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="4" spans="1:17" ht="17.25">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A5" s="7">
-        <v>0</v>
-      </c>
-      <c r="B5" s="8">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>1</v>
-      </c>
-      <c r="H5" s="9">
-        <v>1</v>
-      </c>
-      <c r="I5" s="9">
-        <v>1</v>
-      </c>
-      <c r="K5" s="10" t="s">
+    <row r="5" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A5" s="5">
+        <v>0</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="9">
         <f>MAX(0,SUMPRODUCT(A5:C7,$G$5:$I$7))</f>
         <v>0</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="9">
         <f t="shared" ref="N5:O9" si="0">MAX(0,SUMPRODUCT(B5:D7,$G$5:$I$7))</f>
         <v>5</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A6" s="7">
-        <v>0</v>
-      </c>
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9">
-        <v>1</v>
-      </c>
-      <c r="H6" s="9">
+    <row r="6" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A6" s="5">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
         <v>-10</v>
       </c>
-      <c r="I6" s="9">
-        <v>1</v>
-      </c>
-      <c r="K6" s="12" t="s">
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="9">
         <f t="shared" ref="M6:M9" si="1">MAX(0,SUMPRODUCT(A6:C8,$G$5:$I$7))</f>
         <v>0</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A7" s="7">
-        <v>0</v>
-      </c>
-      <c r="B7" s="8">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9">
-        <v>1</v>
-      </c>
-      <c r="I7" s="9">
-        <v>1</v>
-      </c>
-      <c r="K7" s="12" t="s">
+    <row r="7" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A7" s="5">
+        <v>0</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A8" s="7">
-        <v>0</v>
-      </c>
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-      <c r="K8" s="12" t="s">
+    <row r="8" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A8" s="5">
+        <v>0</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A9" s="7">
-        <v>0</v>
-      </c>
-      <c r="B9" s="8">
-        <v>1</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0</v>
-      </c>
-      <c r="M9" s="11">
+    <row r="9" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A9" s="5">
+        <v>0</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A10" s="7">
-        <v>0</v>
-      </c>
-      <c r="B10" s="8">
-        <v>1</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A11" s="7">
-        <v>0</v>
-      </c>
-      <c r="B11" s="7">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7">
+    <row r="10" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A10" s="5">
+        <v>0</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A11" s="5">
+        <v>0</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="17"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="16"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="19"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="16"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="19"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="16"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="19"/>
     </row>
     <row r="18" spans="1:17" ht="39" customHeight="1">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="20"/>
-    </row>
-    <row r="21" spans="1:17" ht="19.2">
-      <c r="A21" s="6" t="s">
+      <c r="A18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="22"/>
+    </row>
+    <row r="21" spans="1:17" ht="17.25">
+      <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A22" s="7">
-        <v>0</v>
-      </c>
-      <c r="B22" s="8">
-        <v>1</v>
-      </c>
-      <c r="C22" s="8">
-        <v>1</v>
-      </c>
-      <c r="D22" s="8">
-        <v>1</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0</v>
-      </c>
-      <c r="G22" s="9">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9">
-        <v>1</v>
-      </c>
-      <c r="I22" s="9">
-        <v>1</v>
-      </c>
-      <c r="K22" s="10"/>
-      <c r="M22" s="11">
+    <row r="22" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A22" s="5">
+        <v>0</v>
+      </c>
+      <c r="B22" s="6">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7">
+        <v>1</v>
+      </c>
+      <c r="I22" s="7">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8"/>
+      <c r="M22" s="9">
         <f>MAX(0,SUMPRODUCT(A22:C24,$G$5:$I$7))</f>
         <v>0</v>
       </c>
-      <c r="N22" s="21">
+      <c r="N22" s="11">
         <f t="shared" ref="N22:N26" si="2">MAX(0,SUMPRODUCT(B22:D24,$G$5:$I$7))</f>
         <v>8</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="9">
         <f t="shared" ref="O22:O26" si="3">MAX(0,SUMPRODUCT(C22:E24,$G$5:$I$7))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A23" s="7">
-        <v>0</v>
-      </c>
-      <c r="B23" s="8">
-        <v>1</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
-        <v>1</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9">
-        <v>1</v>
-      </c>
-      <c r="H23" s="9">
+    <row r="23" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A23" s="5">
+        <v>0</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7">
         <v>-10</v>
       </c>
-      <c r="I23" s="9">
-        <v>1</v>
-      </c>
-      <c r="K23" s="12"/>
-      <c r="M23" s="11">
+      <c r="I23" s="7">
+        <v>1</v>
+      </c>
+      <c r="K23" s="10"/>
+      <c r="M23" s="9">
         <f t="shared" ref="M23:M26" si="4">MAX(0,SUMPRODUCT(A23:C25,$G$5:$I$7))</f>
         <v>0</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A24" s="7">
-        <v>0</v>
-      </c>
-      <c r="B24" s="8">
-        <v>1</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1</v>
-      </c>
-      <c r="D24" s="8">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>1</v>
-      </c>
-      <c r="H24" s="9">
-        <v>1</v>
-      </c>
-      <c r="I24" s="9">
-        <v>1</v>
-      </c>
-      <c r="K24" s="12"/>
-      <c r="M24" s="11">
+    <row r="24" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A24" s="5">
+        <v>0</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7">
+        <v>1</v>
+      </c>
+      <c r="I24" s="7">
+        <v>1</v>
+      </c>
+      <c r="K24" s="10"/>
+      <c r="M24" s="9">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="9">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A25" s="7">
-        <v>0</v>
-      </c>
-      <c r="B25" s="7">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7">
-        <v>0</v>
-      </c>
-      <c r="D25" s="8">
-        <v>1</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0</v>
-      </c>
-      <c r="K25" s="12"/>
-      <c r="M25" s="11">
+    <row r="25" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A25" s="5">
+        <v>0</v>
+      </c>
+      <c r="B25" s="5">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+      <c r="K25" s="10"/>
+      <c r="M25" s="9">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="N25" s="22">
+      <c r="N25" s="12">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="O25" s="11">
+      <c r="O25" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A26" s="7">
-        <v>0</v>
-      </c>
-      <c r="B26" s="7">
-        <v>0</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0</v>
-      </c>
-      <c r="D26" s="8">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0</v>
-      </c>
-      <c r="M26" s="11">
+    <row r="26" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A26" s="5">
+        <v>0</v>
+      </c>
+      <c r="B26" s="5">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N26" s="11">
+      <c r="N26" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O26" s="11">
+      <c r="O26" s="9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A27" s="7">
-        <v>0</v>
-      </c>
-      <c r="B27" s="8">
-        <v>1</v>
-      </c>
-      <c r="C27" s="8">
-        <v>1</v>
-      </c>
-      <c r="D27" s="8">
-        <v>1</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="22.8" customHeight="1">
-      <c r="A28" s="7">
-        <v>0</v>
-      </c>
-      <c r="B28" s="7">
-        <v>0</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7">
+    <row r="27" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A27" s="5">
+        <v>0</v>
+      </c>
+      <c r="B27" s="6">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="22.9" customHeight="1">
+      <c r="A28" s="5">
+        <v>0</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0</v>
+      </c>
+      <c r="D28" s="5">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5">
         <v>0</v>
       </c>
     </row>

--- a/CNN/CNN.xlsx
+++ b/CNN/CNN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB2AE644-F527-457E-8C85-7D9182A38173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408A8A19-C630-4773-975B-529C1A5E9FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="convolution" sheetId="4" r:id="rId1"/>
     <sheet name="cnn_kernel" sheetId="2" r:id="rId2"/>
     <sheet name="cnn_hole_detector" sheetId="3" r:id="rId3"/>
+    <sheet name="1D Convolution filter" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>1D</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -103,22 +104,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">P(X, Y) = P(X)*P(Y), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서로 독립</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Marginal distribution</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -150,6 +135,93 @@
     <t>Frequency of Z = X  +  Y</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>f1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>f2</t>
+  </si>
+  <si>
+    <t>f3</t>
+  </si>
+  <si>
+    <t>f4</t>
+  </si>
+  <si>
+    <t>f5</t>
+  </si>
+  <si>
+    <t>f6</t>
+  </si>
+  <si>
+    <t>f7</t>
+  </si>
+  <si>
+    <t>f8</t>
+  </si>
+  <si>
+    <t>t+0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>t+1</t>
+  </si>
+  <si>
+    <t>t+2</t>
+  </si>
+  <si>
+    <t>t+3</t>
+  </si>
+  <si>
+    <t>t+4</t>
+  </si>
+  <si>
+    <t>t+5</t>
+  </si>
+  <si>
+    <t>t+6</t>
+  </si>
+  <si>
+    <t>t+7</t>
+  </si>
+  <si>
+    <t>t+8</t>
+  </si>
+  <si>
+    <t>t+9</t>
+  </si>
+  <si>
+    <t>t+10</t>
+  </si>
+  <si>
+    <t>t+11</t>
+  </si>
+  <si>
+    <t>t+12</t>
+  </si>
+  <si>
+    <t>t+13</t>
+  </si>
+  <si>
+    <t>t+14</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">P(X, Y) = P(X)*P(Y), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서로 독립</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -157,8 +229,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="183" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -242,27 +314,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
-      <sz val="12"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="10">
@@ -540,7 +611,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -566,6 +637,9 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -580,57 +654,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -3603,751 +3673,752 @@
   <dimension ref="A2:T27"/>
   <sheetFormatPr defaultRowHeight="17.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="24" customWidth="1"/>
-    <col min="2" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" style="36" customWidth="1"/>
+    <col min="2" max="7" width="6.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="8.5703125" style="25" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A2" s="30" t="s">
-        <v>19</v>
+      <c r="A2" s="24" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="28">
-        <v>1</v>
-      </c>
-      <c r="C3" s="28">
+      <c r="B3" s="27">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27">
         <v>2</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="27">
         <v>3</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="27">
         <v>4</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="27">
         <v>5</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <v>6</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="28" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="30">
         <f>1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="30">
         <f t="shared" ref="C4:G4" si="0">1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="30">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="30">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="30">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="30">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="31">
         <f>SUM(B4:G4)</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A5"/>
+      <c r="A5" s="25"/>
     </row>
     <row r="6" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="28">
-        <v>1</v>
-      </c>
-      <c r="C6" s="28">
+      <c r="B6" s="27">
+        <v>1</v>
+      </c>
+      <c r="C6" s="27">
         <v>2</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="27">
         <v>3</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="27">
         <v>4</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="27">
         <v>5</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="27">
         <v>6</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="28" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="30">
         <f>1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="30">
         <f t="shared" ref="C7:G7" si="1">1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="30">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="30">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="30">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="30">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="31">
         <f>SUM(B7:G7)</f>
         <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A10" s="54"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="55"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
     </row>
     <row r="12" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A12" s="30" t="s">
-        <v>20</v>
+      <c r="A12" s="24" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A13" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13" s="53" t="s">
-        <v>26</v>
+      <c r="A13" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="35" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="35">
-        <v>1</v>
-      </c>
-      <c r="C14" s="35">
+      <c r="B14" s="25">
+        <v>1</v>
+      </c>
+      <c r="C14" s="25">
         <v>2</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="25">
         <v>3</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="25">
         <v>4</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="25">
         <v>5</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="25">
         <v>6</v>
       </c>
-      <c r="L14" s="35">
-        <v>1</v>
-      </c>
-      <c r="M14" s="35">
+      <c r="L14" s="25">
+        <v>1</v>
+      </c>
+      <c r="M14" s="25">
         <v>2</v>
       </c>
-      <c r="N14" s="35">
+      <c r="N14" s="25">
         <v>3</v>
       </c>
-      <c r="O14" s="35">
+      <c r="O14" s="25">
         <v>4</v>
       </c>
-      <c r="P14" s="35">
+      <c r="P14" s="25">
         <v>5</v>
       </c>
-      <c r="Q14" s="35">
+      <c r="Q14" s="25">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A15" s="28">
-        <v>1</v>
-      </c>
-      <c r="B15" s="36">
+      <c r="A15" s="27">
+        <v>1</v>
+      </c>
+      <c r="B15" s="37">
         <f>1/6^2</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f t="shared" ref="C15:G20" si="2">1/6^2</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="38">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="38">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="38">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G15" s="38">
+      <c r="G15" s="39">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="40">
         <f>SUM(B15:G15)</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K15" s="28">
-        <v>1</v>
-      </c>
-      <c r="L15" s="45">
+      <c r="K15" s="27">
+        <v>1</v>
+      </c>
+      <c r="L15" s="41">
         <f>$K15+L$14</f>
         <v>2</v>
       </c>
-      <c r="M15" s="46">
+      <c r="M15" s="42">
         <f t="shared" ref="M15:Q20" si="3">$K15+M$14</f>
         <v>3</v>
       </c>
-      <c r="N15" s="46">
+      <c r="N15" s="42">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="O15" s="46">
+      <c r="O15" s="42">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="P15" s="46">
+      <c r="P15" s="42">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="Q15" s="47">
+      <c r="Q15" s="43">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="17.25" customHeight="1">
-      <c r="A16" s="28">
+      <c r="A16" s="27">
         <v>2</v>
       </c>
-      <c r="B16" s="39">
+      <c r="B16" s="44">
         <f t="shared" ref="B16:B20" si="4">1/6^2</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="46">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="40">
         <f t="shared" ref="H16:H20" si="5">SUM(B16:G16)</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="27">
         <v>2</v>
       </c>
-      <c r="L16" s="48">
+      <c r="L16" s="47">
         <f t="shared" ref="L16:L20" si="6">$K16+L$14</f>
         <v>3</v>
       </c>
-      <c r="M16" s="35">
+      <c r="M16" s="25">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="N16" s="35">
+      <c r="N16" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="O16" s="35">
+      <c r="O16" s="25">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="P16" s="35">
+      <c r="P16" s="25">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="Q16" s="49">
+      <c r="Q16" s="48">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A17" s="28">
+      <c r="A17" s="27">
         <v>3</v>
       </c>
-      <c r="B17" s="39">
+      <c r="B17" s="44">
         <f t="shared" si="4"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="46">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="40">
         <f t="shared" si="5"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="27">
         <v>3</v>
       </c>
-      <c r="L17" s="48">
+      <c r="L17" s="47">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="M17" s="35">
+      <c r="M17" s="25">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N17" s="35">
+      <c r="N17" s="25">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="O17" s="35">
+      <c r="O17" s="25">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="P17" s="35">
+      <c r="P17" s="25">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="Q17" s="49">
+      <c r="Q17" s="48">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A18" s="28">
+      <c r="A18" s="27">
         <v>4</v>
       </c>
-      <c r="B18" s="39">
+      <c r="B18" s="44">
         <f t="shared" si="4"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="46">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="40">
         <f t="shared" si="5"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="27">
         <v>4</v>
       </c>
-      <c r="L18" s="48">
+      <c r="L18" s="47">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="M18" s="35">
+      <c r="M18" s="25">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="N18" s="35">
+      <c r="N18" s="25">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="O18" s="35">
+      <c r="O18" s="25">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="P18" s="35">
+      <c r="P18" s="25">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="Q18" s="49">
+      <c r="Q18" s="48">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A19" s="28">
+      <c r="A19" s="27">
         <v>5</v>
       </c>
-      <c r="B19" s="39">
+      <c r="B19" s="44">
         <f t="shared" si="4"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="45">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="46">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="40">
         <f t="shared" si="5"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="27">
         <v>5</v>
       </c>
-      <c r="L19" s="48">
+      <c r="L19" s="47">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="M19" s="35">
+      <c r="M19" s="25">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="N19" s="35">
+      <c r="N19" s="25">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="O19" s="35">
+      <c r="O19" s="25">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="P19" s="35">
+      <c r="P19" s="25">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="Q19" s="49">
+      <c r="Q19" s="48">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A20" s="28">
+      <c r="A20" s="27">
         <v>6</v>
       </c>
-      <c r="B20" s="42">
+      <c r="B20" s="49">
         <f t="shared" si="4"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="50">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="50">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="50">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="50">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="51">
         <f t="shared" si="2"/>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="40">
         <f t="shared" si="5"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="27">
         <v>6</v>
       </c>
-      <c r="L20" s="50">
+      <c r="L20" s="52">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="M20" s="51">
+      <c r="M20" s="53">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="N20" s="51">
+      <c r="N20" s="53">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="O20" s="51">
+      <c r="O20" s="53">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="P20" s="51">
+      <c r="P20" s="53">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="Q20" s="52">
+      <c r="Q20" s="54">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="17.25" customHeight="1">
-      <c r="B21" s="31">
+      <c r="B21" s="45">
         <f>SUM(B15:B20)</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="45">
         <f t="shared" ref="C21:G21" si="7">SUM(C15:C20)</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="45">
         <f t="shared" si="7"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="45">
         <f t="shared" si="7"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="45">
         <f t="shared" si="7"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="45">
         <f t="shared" si="7"/>
         <v>0.16666666666666669</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="40">
         <f>SUM(B15:G20)</f>
         <v>1.0000000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="17.25" customHeight="1">
-      <c r="H22" s="32"/>
+      <c r="H22" s="40"/>
     </row>
     <row r="23" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>25</v>
+      <c r="A23" s="24" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>21</v>
+      <c r="A24" s="34" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="27">
+        <v>2</v>
+      </c>
+      <c r="C25" s="27">
+        <v>3</v>
+      </c>
+      <c r="D25" s="27">
+        <v>4</v>
+      </c>
+      <c r="E25" s="27">
+        <v>5</v>
+      </c>
+      <c r="F25" s="27">
+        <v>6</v>
+      </c>
+      <c r="G25" s="27">
+        <v>7</v>
+      </c>
+      <c r="H25" s="27">
+        <v>8</v>
+      </c>
+      <c r="I25" s="27">
+        <v>9</v>
+      </c>
+      <c r="J25" s="27">
+        <v>10</v>
+      </c>
+      <c r="K25" s="27">
+        <v>11</v>
+      </c>
+      <c r="L25" s="27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="17.25" customHeight="1">
+      <c r="A26" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="28">
-        <v>2</v>
-      </c>
-      <c r="C25" s="28">
-        <v>3</v>
-      </c>
-      <c r="D25" s="28">
-        <v>4</v>
-      </c>
-      <c r="E25" s="28">
-        <v>5</v>
-      </c>
-      <c r="F25" s="28">
-        <v>6</v>
-      </c>
-      <c r="G25" s="28">
-        <v>7</v>
-      </c>
-      <c r="H25" s="28">
-        <v>8</v>
-      </c>
-      <c r="I25" s="28">
-        <v>9</v>
-      </c>
-      <c r="J25" s="28">
-        <v>10</v>
-      </c>
-      <c r="K25" s="28">
-        <v>11</v>
-      </c>
-      <c r="L25" s="28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A26" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26">
+      <c r="B26" s="25">
         <f>COUNTIF($L$15:$Q$20, B25)</f>
         <v>1</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="25">
         <f t="shared" ref="C26:L26" si="8">COUNTIF($L$15:$Q$20, C25)</f>
         <v>2</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="25">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="25">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="25">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="25">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="25">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="25">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="25">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="25">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="25">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="17.25" customHeight="1">
-      <c r="A27" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="A27" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="45">
         <f>B26/COUNT($L$15:$Q$20)</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="45">
         <f t="shared" ref="C27:L27" si="9">C26/COUNT($L$15:$Q$20)</f>
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="45">
         <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="45">
         <f t="shared" si="9"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="45">
         <f t="shared" si="9"/>
         <v>0.1388888888888889</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="45">
         <f t="shared" si="9"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="45">
         <f t="shared" si="9"/>
         <v>0.1388888888888889</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="45">
         <f t="shared" si="9"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="45">
         <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="45">
         <f t="shared" si="9"/>
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="45">
         <f t="shared" si="9"/>
         <v>2.7777777777777776E-2</v>
       </c>
@@ -4364,7 +4435,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B2:Y49"/>
+  <dimension ref="B2:Y16"/>
   <sheetFormatPr defaultColWidth="6.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="2" spans="2:25">
@@ -5227,271 +5298,6 @@
       <c r="I16" s="2">
         <f t="shared" si="27"/>
         <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="9:20">
-      <c r="I19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2">
-        <f>1</f>
-        <v>1</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19" s="2">
-        <f>L19+1</f>
-        <v>1</v>
-      </c>
-      <c r="N19" s="2">
-        <v>0</v>
-      </c>
-      <c r="O19" s="2">
-        <f>N19+1</f>
-        <v>1</v>
-      </c>
-      <c r="P19" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="2">
-        <f>P19+1</f>
-        <v>1</v>
-      </c>
-      <c r="R19" s="2">
-        <v>0</v>
-      </c>
-      <c r="T19" s="1">
-        <f t="shared" ref="T19:T33" si="28">SUMPRODUCT(B2:I2,$K$19:$R$19)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="9:20">
-      <c r="T20" s="1">
-        <f t="shared" si="28"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="9:20">
-      <c r="T21" s="1">
-        <f t="shared" si="28"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="9:20">
-      <c r="T22" s="1">
-        <f t="shared" si="28"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="9:20">
-      <c r="T23" s="1">
-        <f t="shared" si="28"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="9:20">
-      <c r="T24" s="1">
-        <f t="shared" si="28"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="9:20">
-      <c r="T25" s="1">
-        <f t="shared" si="28"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="9:20">
-      <c r="T26" s="1">
-        <f t="shared" si="28"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="9:20">
-      <c r="T27" s="1">
-        <f t="shared" si="28"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="9:20">
-      <c r="T28" s="1">
-        <f t="shared" si="28"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="9:20">
-      <c r="T29" s="1">
-        <f t="shared" si="28"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="9:20">
-      <c r="T30" s="1">
-        <f t="shared" si="28"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="9:20">
-      <c r="T31" s="1">
-        <f t="shared" si="28"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="9:20">
-      <c r="T32" s="1">
-        <f t="shared" si="28"/>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="9:20">
-      <c r="T33" s="1">
-        <f t="shared" si="28"/>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="9:20">
-      <c r="I36" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2">
-        <f>1</f>
-        <v>1</v>
-      </c>
-      <c r="L36" s="2">
-        <v>0</v>
-      </c>
-      <c r="M36" s="2">
-        <f>L36+1</f>
-        <v>1</v>
-      </c>
-      <c r="N36" s="2">
-        <v>0</v>
-      </c>
-      <c r="O36" s="2">
-        <f>N36+1</f>
-        <v>1</v>
-      </c>
-      <c r="P36" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="2">
-        <f>P36+1</f>
-        <v>1</v>
-      </c>
-      <c r="R36" s="2">
-        <v>0</v>
-      </c>
-      <c r="T36" s="1">
-        <f t="shared" ref="T36:T49" si="29">SUMPRODUCT(B2:I3, $K$36:$R$37)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="9:20">
-      <c r="K37" s="2">
-        <v>0</v>
-      </c>
-      <c r="L37" s="2">
-        <f>K37+1</f>
-        <v>1</v>
-      </c>
-      <c r="M37" s="2">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2">
-        <f>M37+1</f>
-        <v>1</v>
-      </c>
-      <c r="O37" s="2">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2">
-        <f>O37+1</f>
-        <v>1</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>0</v>
-      </c>
-      <c r="R37" s="2">
-        <f>Q37+1</f>
-        <v>1</v>
-      </c>
-      <c r="T37" s="1">
-        <f t="shared" si="29"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="9:20">
-      <c r="T38" s="1">
-        <f t="shared" si="29"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="9:20">
-      <c r="T39" s="1">
-        <f t="shared" si="29"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="9:20">
-      <c r="T40" s="1">
-        <f t="shared" si="29"/>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="9:20">
-      <c r="T41" s="1">
-        <f t="shared" si="29"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="9:20">
-      <c r="T42" s="1">
-        <f t="shared" si="29"/>
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="9:20">
-      <c r="T43" s="1">
-        <f t="shared" si="29"/>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="9:20">
-      <c r="T44" s="1">
-        <f t="shared" si="29"/>
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="9:20">
-      <c r="T45" s="1">
-        <f t="shared" si="29"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="9:20">
-      <c r="T46" s="1">
-        <f t="shared" si="29"/>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="9:20">
-      <c r="T47" s="1">
-        <f t="shared" si="29"/>
-        <v>128</v>
-      </c>
-    </row>
-    <row r="48" spans="9:20">
-      <c r="T48" s="1">
-        <f t="shared" si="29"/>
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="20:20">
-      <c r="T49" s="1">
-        <f t="shared" si="29"/>
-        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -5516,44 +5322,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
+      <c r="A1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
     </row>
     <row r="4" spans="1:17" ht="17.25">
       <c r="A4" s="4" t="s">
@@ -5788,101 +5594,101 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="18"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="18"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="19"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="20"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="18"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="19"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="20"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="18"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="19"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="20"/>
     </row>
     <row r="18" spans="1:17" ht="39" customHeight="1">
-      <c r="A18" s="20"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="23"/>
     </row>
     <row r="21" spans="1:17" ht="17.25">
       <c r="A21" s="4" t="s">
@@ -6116,4 +5922,1038 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627979F7-11C8-418A-8E8F-A1FF52374681}">
+  <dimension ref="A4:Y49"/>
+  <sheetFormatPr defaultColWidth="6.42578125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="22" max="22" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:25">
+      <c r="B4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <f>N4+1</f>
+        <v>1</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>P4+1</f>
+        <v>1</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <f>R4+1</f>
+        <v>1</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
+        <f>SUMPRODUCT(B5:I5,$M$4:$T$4)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" ref="C5:I5" si="0">B5+1</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="V5" s="1">
+        <f>SUMPRODUCT(B6:I6,$M$4:$T$4)</f>
+        <v>20</v>
+      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" ref="B6:I19" si="1">B5+1</f>
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="V6" s="1">
+        <f>SUMPRODUCT(B7:I7,$M$4:$T$4)</f>
+        <v>24</v>
+      </c>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="V7" s="1">
+        <f>SUMPRODUCT(B8:I8,$M$4:$T$4)</f>
+        <v>28</v>
+      </c>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="V8" s="1">
+        <f>SUMPRODUCT(B9:I9,$M$4:$T$4)</f>
+        <v>32</v>
+      </c>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="2">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="V9" s="1">
+        <f>SUMPRODUCT(B10:I10,$M$4:$T$4)</f>
+        <v>36</v>
+      </c>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="V10" s="1">
+        <f>SUMPRODUCT(B11:I11,$M$4:$T$4)</f>
+        <v>40</v>
+      </c>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="V11" s="1">
+        <f>SUMPRODUCT(B12:I12,$M$4:$T$4)</f>
+        <v>44</v>
+      </c>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="V12" s="1">
+        <f>SUMPRODUCT(B13:I13,$M$4:$T$4)</f>
+        <v>48</v>
+      </c>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="V13" s="1">
+        <f>SUMPRODUCT(B14:I14,$M$4:$T$4)</f>
+        <v>52</v>
+      </c>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="V14" s="1">
+        <f>SUMPRODUCT(B15:I15,$M$4:$T$4)</f>
+        <v>56</v>
+      </c>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="V15" s="1">
+        <f>SUMPRODUCT(B16:I16,$M$4:$T$4)</f>
+        <v>60</v>
+      </c>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="V16" s="1">
+        <f>SUMPRODUCT(B17:I17,$M$4:$T$4)</f>
+        <v>64</v>
+      </c>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="V17" s="1">
+        <f>SUMPRODUCT(B18:I18,$M$4:$T$4)</f>
+        <v>68</v>
+      </c>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="C18" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="V18" s="1">
+        <f>SUMPRODUCT(B19:I19,$M$4:$T$4)</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="K21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="N21" s="2">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2">
+        <f>N21+1</f>
+        <v>1</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <f>P21+1</f>
+        <v>1</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <f>R21+1</f>
+        <v>1</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
+        <f>SUMPRODUCT(B5:I6, $M$21:$T$22)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
+        <f>M22+1</f>
+        <v>1</v>
+      </c>
+      <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
+        <f>O22+1</f>
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
+        <f>Q22+1</f>
+        <v>1</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
+        <f>S22+1</f>
+        <v>1</v>
+      </c>
+      <c r="V22" s="1">
+        <f>SUMPRODUCT(B6:I7, $M$21:$T$22)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="V23" s="1">
+        <f>SUMPRODUCT(B7:I8, $M$21:$T$22)</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="V24" s="1">
+        <f>SUMPRODUCT(B8:I9, $M$21:$T$22)</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="V25" s="1">
+        <f>SUMPRODUCT(B9:I10, $M$21:$T$22)</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="V26" s="1">
+        <f>SUMPRODUCT(B10:I11, $M$21:$T$22)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="V27" s="1">
+        <f>SUMPRODUCT(B11:I12, $M$21:$T$22)</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="V28" s="1">
+        <f>SUMPRODUCT(B12:I13, $M$21:$T$22)</f>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="V29" s="1">
+        <f>SUMPRODUCT(B13:I14, $M$21:$T$22)</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="V30" s="1">
+        <f>SUMPRODUCT(B14:I15, $M$21:$T$22)</f>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="V31" s="1">
+        <f>SUMPRODUCT(B15:I16, $M$21:$T$22)</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="V32" s="1">
+        <f>SUMPRODUCT(B16:I17, $M$21:$T$22)</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="11:22">
+      <c r="V33" s="1">
+        <f>SUMPRODUCT(B17:I18, $M$21:$T$22)</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="11:22">
+      <c r="V34" s="1">
+        <f>SUMPRODUCT(B18:I19, $M$21:$T$22)</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="11:22">
+      <c r="K37" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2">
+        <f>N37+1</f>
+        <v>1</v>
+      </c>
+      <c r="P37" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2">
+        <f>P37+1</f>
+        <v>1</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
+        <f>R37+1</f>
+        <v>1</v>
+      </c>
+      <c r="T37" s="2">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <f>SUMPRODUCT(B5:I7, $M$37:$T$39)</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="11:22">
+      <c r="M38" s="2">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2">
+        <f>M38+1</f>
+        <v>1</v>
+      </c>
+      <c r="O38" s="2">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2">
+        <f>O38+1</f>
+        <v>1</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2">
+        <f>Q38+1</f>
+        <v>1</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2">
+        <f>S38+1</f>
+        <v>1</v>
+      </c>
+      <c r="V38">
+        <f t="shared" ref="V38:V43" si="2">SUMPRODUCT(B6:I8, $M$37:$T$39)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="11:22">
+      <c r="M39" s="2">
+        <f>1</f>
+        <v>1</v>
+      </c>
+      <c r="N39" s="2">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2">
+        <f>N39+1</f>
+        <v>1</v>
+      </c>
+      <c r="P39" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2">
+        <f>P39+1</f>
+        <v>1</v>
+      </c>
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2">
+        <f>R39+1</f>
+        <v>1</v>
+      </c>
+      <c r="T39" s="2">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="11:22">
+      <c r="V40">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="11:22">
+      <c r="V41">
+        <f t="shared" si="2"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="11:22">
+      <c r="V42">
+        <f t="shared" si="2"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="11:22">
+      <c r="V43">
+        <f>SUMPRODUCT(B11:I13, $M$37:$T$39)</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="11:22">
+      <c r="V44">
+        <f t="shared" ref="V44:V47" si="3">SUMPRODUCT(B12:I14, $M$37:$T$39)</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="11:22">
+      <c r="V45">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="11:22">
+      <c r="V46">
+        <f t="shared" si="3"/>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="47" spans="11:22">
+      <c r="V47">
+        <f>SUMPRODUCT(B15:I17, $M$37:$T$39)</f>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="11:22">
+      <c r="V48">
+        <f t="shared" ref="V48:V49" si="4">SUMPRODUCT(B16:I18, $M$37:$T$39)</f>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="22:22">
+      <c r="V49">
+        <f>SUMPRODUCT(B17:I19, $M$37:$T$39)</f>
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>